--- a/4994_Cuenca_Urubamba/_raw_reportes_xlsx/IDConfig_65379_completo.xlsx
+++ b/4994_Cuenca_Urubamba/_raw_reportes_xlsx/IDConfig_65379_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra80740cb12634ba4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R315615ee75bd4adb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1983</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2075</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2167</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2558</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3808</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3508</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3279</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3192</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/4994_Cuenca_Urubamba/_raw_reportes_xlsx/IDConfig_65379_completo.xlsx
+++ b/4994_Cuenca_Urubamba/_raw_reportes_xlsx/IDConfig_65379_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R315615ee75bd4adb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb2631699041f4b4c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4279</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4221</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3283</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3246</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3167</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3296</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4021</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4392</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4158</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4158</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4104</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3271</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3304</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3279</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3283</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3296</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3475</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2279</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3808</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3938</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4092</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4138</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4038</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3983</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3721</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3588</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3538</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3513</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3363</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2021</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1839</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1742</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1746</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1733</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1613</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1667</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1904</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1927</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2075</x:v>
+        <x:v>      0.1975</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2167</x:v>
+        <x:v>      0.2067</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2558</x:v>
+        <x:v>      0.2458</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3808</x:v>
+        <x:v>      0.3708</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3308</x:v>
+        <x:v>      0.3358</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3325</x:v>
+        <x:v>      0.3225</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3375</x:v>
+        <x:v>      0.3225</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3179</x:v>
+        <x:v>      0.3150</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3242</x:v>
+        <x:v>      0.3142</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3263</x:v>
+        <x:v>      0.3163</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3250</x:v>
+        <x:v>      0.3150</x:v>
       </x:c>
     </x:row>
     <x:row>
